--- a/Sep_2026/Daily Sale/28-09-26/Zeshan.xlsx
+++ b/Sep_2026/Daily Sale/28-09-26/Zeshan.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29127"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7001E89-4D8E-4107-9EB8-E69F0DEA2326}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D79D8E62-55C7-4988-83AE-1A10D55FDAEC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="948" firstSheet="3" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -47939,7 +47939,7 @@
       <c r="L4" s="371"/>
       <c r="M4" s="401">
         <f ca="1">TODAY()+1</f>
-        <v>46294</v>
+        <v>46296</v>
       </c>
       <c r="N4" s="401"/>
       <c r="O4" s="401"/>
@@ -47967,7 +47967,7 @@
       <c r="L5" s="371"/>
       <c r="M5" s="401">
         <f ca="1">M4-1</f>
-        <v>46293</v>
+        <v>46295</v>
       </c>
       <c r="N5" s="370"/>
       <c r="O5" s="370"/>
